--- a/pharmacist_forms/001_pharmacy_employee_performance_review_form--pharmacist_forms.xlsx
+++ b/pharmacist_forms/001_pharmacy_employee_performance_review_form--pharmacist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>overall_performance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>page_1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Overall Performance</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rate the employee's overall performance.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,41 +547,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rating_1</t>
+          <t>skills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Employee Skills</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate the employee's skills.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rating_2</t>
+          <t>areas_for_improvement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Areas for Improvement</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe any areas where the employee needs improvement.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,513 +601,589 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rating_3</t>
+          <t>overall_rating</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Overall Rating</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rate the employee's overall performance.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rating_4</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Time Management</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rate the employee's time management skills.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rating_5</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Customer Service</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Select one of the following</t>
+          <t>Rate the employee's customer service skills.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rating_6</t>
+          <t>initiative</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Initiative</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rate the employee's initiative in taking on additional responsibilities.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rating_7</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rate the employee's communication skills with colleagues and customers.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rating_8</t>
+          <t>company_policies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Company Policies</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rate the employee's adherence to company policies and procedures.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rating_9</t>
+          <t>punctuality</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Punctuality</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rate the employee's punctuality and reliability.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rating_10</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Teamwork</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rate the employee's teamwork and collaboration with colleagues.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rating_11</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Adaptability</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rate the employee's adaptability and flexibility in their work environment.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rating_12</t>
+          <t>quality_assurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Rate the employee's commitment to quality assurance in their work.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rating_13</t>
+          <t>safety_and_accuracy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Safety and Accuracy</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Rate the employee's commitment to safety and accuracy in their work.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rating_14</t>
+          <t>cleanliness</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Cleanliness</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Rate the employee's commitment to maintaining a clean and organized workspace.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rating_15</t>
+          <t>confidentiality</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Confidentiality</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Rate the employee's commitment to maintaining confidentiality and security in their work.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rating_16</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Add any additional comments or suggestions for the employee.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rating_17</t>
+          <t>continuous_learning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Continuous Learning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Rate the employee's commitment to continuous learning and professional development.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rating_18</t>
+          <t>customer_satisfaction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Customer Satisfaction</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Rate the employee's commitment to customer satisfaction.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rating_19</t>
+          <t>conflict_resolution</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Conflict Resolution</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Rate the employee's conflict resolution skills.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rating_20</t>
+          <t>continuous_improvement</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Continuous Improvement</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Rate the employee's commitment to continuous improvement in their work.</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>rating_21</t>
+          <t>overall_attitude</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Overall Attitude</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Select one of the following</t>
+          <t>Rate the employee's overall attitude towards their work.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>rating_22</t>
+          <t>punctuality_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Punctuality 2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Rate the employee's punctuality and reliability.</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rating_23</t>
+          <t>employee_suggestion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Employee's Suggestion</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Add any suggestions from the employee to improve their performance.</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rating_24</t>
+          <t>final_comments</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Final Comments</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Select one of the following</t>
+          <t>Add any final comments or suggestions for the employee.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1198,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1138,918 +1226,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rating_1_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rating_1_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rating_2_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rating_2_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rating_3_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rating_3_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rating_4_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>rating_4_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>rating_5_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>rating_5_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>rating_5_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>rating_5_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>rating_6_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>rating_6_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>rating_7_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>rating_7_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>rating_8_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>rating_8_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>rating_9_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>rating_9_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>rating_10_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>rating_10_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>rating_11_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>rating_11_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>rating_12_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>rating_12_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>rating_13_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>rating_13_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>rating_14_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>rating_14_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>rating_15_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>rating_15_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>rating_16_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>rating_16_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>rating_17_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>rating_17_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>rating_18_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>rating_18_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>rating_19_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>rating_19_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>rating_20_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>rating_20_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>rating_21_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>rating_21_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>rating_21_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>rating_21_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>rating_22_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>rating_22_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>rating_23_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>rating_23_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>rating_24_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>rating_24_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>rating_24_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>rating_24_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Poor</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
